--- a/AAII_Financials/Quarterly/OMCC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/OMCC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="92">
   <si>
     <t>OMCC</t>
   </si>
@@ -959,7 +959,7 @@
         <v>0</v>
       </c>
       <c r="F14" s="3">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="G14" s="3">
         <v>0</v>
@@ -1055,7 +1055,7 @@
         <v>4000</v>
       </c>
       <c r="F17" s="3">
-        <v>4400</v>
+        <v>3300</v>
       </c>
       <c r="G17" s="3">
         <v>3700</v>
@@ -1096,7 +1096,7 @@
         <v>-1000</v>
       </c>
       <c r="F18" s="3">
-        <v>-1400</v>
+        <v>-300</v>
       </c>
       <c r="G18" s="3">
         <v>-700</v>
@@ -1154,7 +1154,7 @@
         <v>0</v>
       </c>
       <c r="F20" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="G20" s="3">
         <v>0</v>
@@ -1195,7 +1195,7 @@
         <v>-400</v>
       </c>
       <c r="F21" s="3">
-        <v>-500</v>
+        <v>700</v>
       </c>
       <c r="G21" s="3">
         <v>-200</v>
@@ -1646,7 +1646,7 @@
         <v>0</v>
       </c>
       <c r="F32" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G32" s="3">
         <v>0</v>
@@ -2696,14 +2696,14 @@
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>12100</v>
+      <c r="D62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E62" s="3">
         <v>13900</v>
       </c>
-      <c r="F62" s="3">
-        <v>13900</v>
+      <c r="F62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G62" s="3">
         <v>14200</v>
@@ -2861,13 +2861,13 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>27300</v>
+        <v>15200</v>
       </c>
       <c r="E66" s="3">
         <v>26500</v>
       </c>
       <c r="F66" s="3">
-        <v>24500</v>
+        <v>10700</v>
       </c>
       <c r="G66" s="3">
         <v>25500</v>
